--- a/aaa0769_1to1_replaceable_pairs_complementing.xlsx
+++ b/aaa0769_1to1_replaceable_pairs_complementing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unilj-my.sharepoint.com/personal/bk1118_student_uni-lj_si/Documents/IJS/članki/Tarče za tarčno degradacijo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2843320FE81B954308F5439B20170A1FC2766718" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F75F681-65F7-40CC-8366-05786313DDC7}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2843320FE81B954308F5439B20170A1FC2766718" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00F2FC28-ED52-4EB6-80DF-D29FB44BC01D}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Replaceable_200" sheetId="1" r:id="rId1"/>
@@ -2354,9 +2354,6 @@
     <t>YOR244W</t>
   </si>
   <si>
-    <t>ENSP00000340330</t>
-  </si>
-  <si>
     <t>10524</t>
   </si>
   <si>
@@ -3096,6 +3093,9 @@
   </si>
   <si>
     <t>phosphatidylinositol glycan anchor biosynthesis, class A</t>
+  </si>
+  <si>
+    <t>9OT6,8DP0,5DFZ,8DCP,8DCX,8DD4,8DD8</t>
   </si>
 </sst>
 </file>
@@ -3462,6 +3462,8 @@
   <dimension ref="A1:N201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="106.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8172,16 +8174,16 @@
         <v>776</v>
       </c>
       <c r="B153" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C153" t="s">
         <v>777</v>
       </c>
-      <c r="C153" t="s">
+      <c r="D153" t="s">
         <v>778</v>
       </c>
-      <c r="D153" t="s">
+      <c r="E153" t="s">
         <v>779</v>
-      </c>
-      <c r="E153" t="s">
-        <v>780</v>
       </c>
       <c r="F153" t="s">
         <v>19</v>
@@ -8195,19 +8197,19 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>780</v>
+      </c>
+      <c r="B154" t="s">
         <v>781</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" t="s">
         <v>782</v>
       </c>
-      <c r="C154" t="s">
+      <c r="D154" t="s">
         <v>783</v>
       </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
         <v>784</v>
-      </c>
-      <c r="E154" t="s">
-        <v>785</v>
       </c>
       <c r="F154" t="s">
         <v>19</v>
@@ -8233,19 +8235,19 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>785</v>
+      </c>
+      <c r="B155" t="s">
         <v>786</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" t="s">
         <v>787</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D155" t="s">
         <v>788</v>
       </c>
-      <c r="D155" t="s">
+      <c r="E155" t="s">
         <v>789</v>
-      </c>
-      <c r="E155" t="s">
-        <v>790</v>
       </c>
       <c r="F155" t="s">
         <v>19</v>
@@ -8262,19 +8264,19 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>790</v>
+      </c>
+      <c r="B156" t="s">
         <v>791</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" t="s">
         <v>792</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
         <v>793</v>
       </c>
-      <c r="D156" t="s">
+      <c r="E156" t="s">
         <v>794</v>
-      </c>
-      <c r="E156" t="s">
-        <v>795</v>
       </c>
       <c r="F156" t="s">
         <v>19</v>
@@ -8291,19 +8293,19 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>795</v>
+      </c>
+      <c r="B157" t="s">
         <v>796</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
         <v>797</v>
       </c>
-      <c r="C157" t="s">
+      <c r="D157" t="s">
         <v>798</v>
       </c>
-      <c r="D157" t="s">
+      <c r="E157" t="s">
         <v>799</v>
-      </c>
-      <c r="E157" t="s">
-        <v>800</v>
       </c>
       <c r="F157" t="s">
         <v>19</v>
@@ -8320,19 +8322,19 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>800</v>
+      </c>
+      <c r="B158" t="s">
         <v>801</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
         <v>802</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D158" t="s">
         <v>803</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
         <v>804</v>
-      </c>
-      <c r="E158" t="s">
-        <v>805</v>
       </c>
       <c r="F158" t="s">
         <v>19</v>
@@ -8352,19 +8354,19 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>805</v>
+      </c>
+      <c r="B159" t="s">
         <v>806</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>807</v>
       </c>
-      <c r="C159" t="s">
+      <c r="D159" t="s">
         <v>808</v>
       </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
         <v>809</v>
-      </c>
-      <c r="E159" t="s">
-        <v>810</v>
       </c>
       <c r="F159" t="s">
         <v>19</v>
@@ -8381,19 +8383,19 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>810</v>
+      </c>
+      <c r="B160" t="s">
         <v>811</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" t="s">
         <v>812</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
         <v>813</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
         <v>814</v>
-      </c>
-      <c r="E160" t="s">
-        <v>815</v>
       </c>
       <c r="F160" t="s">
         <v>19</v>
@@ -8416,19 +8418,19 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>815</v>
+      </c>
+      <c r="B161" t="s">
         <v>816</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" t="s">
         <v>817</v>
       </c>
-      <c r="C161" t="s">
+      <c r="D161" t="s">
         <v>818</v>
       </c>
-      <c r="D161" t="s">
+      <c r="E161" t="s">
         <v>819</v>
-      </c>
-      <c r="E161" t="s">
-        <v>820</v>
       </c>
       <c r="F161" t="s">
         <v>19</v>
@@ -8445,19 +8447,19 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>820</v>
+      </c>
+      <c r="B162" t="s">
         <v>821</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>822</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
         <v>823</v>
       </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
         <v>824</v>
-      </c>
-      <c r="E162" t="s">
-        <v>825</v>
       </c>
       <c r="F162" t="s">
         <v>19</v>
@@ -8474,19 +8476,19 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>825</v>
+      </c>
+      <c r="B163" t="s">
         <v>826</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" t="s">
         <v>827</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163" t="s">
         <v>828</v>
       </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
         <v>829</v>
-      </c>
-      <c r="E163" t="s">
-        <v>830</v>
       </c>
       <c r="F163" t="s">
         <v>19</v>
@@ -8509,19 +8511,19 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>830</v>
+      </c>
+      <c r="B164" t="s">
         <v>831</v>
       </c>
-      <c r="B164" t="s">
+      <c r="C164" t="s">
         <v>832</v>
       </c>
-      <c r="C164" t="s">
+      <c r="D164" t="s">
         <v>833</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
         <v>834</v>
-      </c>
-      <c r="E164" t="s">
-        <v>835</v>
       </c>
       <c r="F164" t="s">
         <v>19</v>
@@ -8535,19 +8537,19 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>835</v>
+      </c>
+      <c r="B165" t="s">
         <v>836</v>
       </c>
-      <c r="B165" t="s">
+      <c r="C165" t="s">
         <v>837</v>
       </c>
-      <c r="C165" t="s">
+      <c r="D165" t="s">
         <v>838</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
         <v>839</v>
-      </c>
-      <c r="E165" t="s">
-        <v>840</v>
       </c>
       <c r="F165" t="s">
         <v>19</v>
@@ -8570,19 +8572,19 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>840</v>
+      </c>
+      <c r="B166" t="s">
         <v>841</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>842</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
         <v>843</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
         <v>844</v>
-      </c>
-      <c r="E166" t="s">
-        <v>845</v>
       </c>
       <c r="F166" t="s">
         <v>19</v>
@@ -8602,19 +8604,19 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>845</v>
+      </c>
+      <c r="B167" t="s">
         <v>846</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C167" t="s">
         <v>847</v>
       </c>
-      <c r="C167" t="s">
+      <c r="D167" t="s">
         <v>848</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>849</v>
-      </c>
-      <c r="E167" t="s">
-        <v>850</v>
       </c>
       <c r="F167" t="s">
         <v>19</v>
@@ -8631,19 +8633,19 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>850</v>
+      </c>
+      <c r="B168" t="s">
         <v>851</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
         <v>852</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168" t="s">
         <v>853</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
         <v>854</v>
-      </c>
-      <c r="E168" t="s">
-        <v>855</v>
       </c>
       <c r="F168" t="s">
         <v>19</v>
@@ -8660,19 +8662,19 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>855</v>
+      </c>
+      <c r="B169" t="s">
         <v>856</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" t="s">
         <v>857</v>
       </c>
-      <c r="C169" t="s">
+      <c r="D169" t="s">
         <v>858</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
         <v>859</v>
-      </c>
-      <c r="E169" t="s">
-        <v>860</v>
       </c>
       <c r="F169" t="s">
         <v>19</v>
@@ -8698,19 +8700,19 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>860</v>
+      </c>
+      <c r="B170" t="s">
         <v>861</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C170" t="s">
         <v>862</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>863</v>
       </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
         <v>864</v>
-      </c>
-      <c r="E170" t="s">
-        <v>865</v>
       </c>
       <c r="F170" t="s">
         <v>19</v>
@@ -8730,19 +8732,19 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>865</v>
+      </c>
+      <c r="B171" t="s">
         <v>866</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
         <v>867</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
         <v>868</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E171" t="s">
         <v>869</v>
-      </c>
-      <c r="E171" t="s">
-        <v>870</v>
       </c>
       <c r="F171" t="s">
         <v>19</v>
@@ -8765,19 +8767,19 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>870</v>
+      </c>
+      <c r="B172" t="s">
         <v>871</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>872</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
         <v>873</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" t="s">
         <v>874</v>
-      </c>
-      <c r="E172" t="s">
-        <v>875</v>
       </c>
       <c r="F172" t="s">
         <v>19</v>
@@ -8794,19 +8796,19 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>875</v>
+      </c>
+      <c r="B173" t="s">
         <v>876</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
         <v>877</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
         <v>878</v>
       </c>
-      <c r="D173" t="s">
+      <c r="E173" t="s">
         <v>879</v>
-      </c>
-      <c r="E173" t="s">
-        <v>880</v>
       </c>
       <c r="F173" t="s">
         <v>19</v>
@@ -8823,19 +8825,19 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>880</v>
+      </c>
+      <c r="B174" t="s">
         <v>881</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>882</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
         <v>883</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>884</v>
-      </c>
-      <c r="E174" t="s">
-        <v>885</v>
       </c>
       <c r="F174" t="s">
         <v>19</v>
@@ -8849,19 +8851,19 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>885</v>
+      </c>
+      <c r="B175" t="s">
         <v>886</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>887</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
         <v>888</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>889</v>
-      </c>
-      <c r="E175" t="s">
-        <v>890</v>
       </c>
       <c r="F175" t="s">
         <v>19</v>
@@ -8887,19 +8889,19 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>890</v>
+      </c>
+      <c r="B176" t="s">
         <v>891</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
         <v>892</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
         <v>893</v>
       </c>
-      <c r="D176" t="s">
+      <c r="E176" t="s">
         <v>894</v>
-      </c>
-      <c r="E176" t="s">
-        <v>895</v>
       </c>
       <c r="F176" t="s">
         <v>19</v>
@@ -8919,19 +8921,19 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>895</v>
+      </c>
+      <c r="B177" t="s">
         <v>896</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
         <v>897</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
         <v>898</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>899</v>
-      </c>
-      <c r="E177" t="s">
-        <v>900</v>
       </c>
       <c r="F177" t="s">
         <v>19</v>
@@ -8948,19 +8950,19 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>900</v>
+      </c>
+      <c r="B178" t="s">
         <v>901</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>902</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
         <v>903</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>904</v>
-      </c>
-      <c r="E178" t="s">
-        <v>905</v>
       </c>
       <c r="F178" t="s">
         <v>19</v>
@@ -8977,19 +8979,19 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>905</v>
+      </c>
+      <c r="B179" t="s">
         <v>906</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>907</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
         <v>908</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
         <v>909</v>
-      </c>
-      <c r="E179" t="s">
-        <v>910</v>
       </c>
       <c r="F179" t="s">
         <v>19</v>
@@ -9003,19 +9005,19 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>910</v>
+      </c>
+      <c r="B180" t="s">
         <v>911</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>912</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
         <v>913</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
         <v>914</v>
-      </c>
-      <c r="E180" t="s">
-        <v>915</v>
       </c>
       <c r="F180" t="s">
         <v>19</v>
@@ -9029,19 +9031,19 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>915</v>
+      </c>
+      <c r="B181" t="s">
         <v>916</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>917</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D181" t="s">
         <v>918</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>919</v>
-      </c>
-      <c r="E181" t="s">
-        <v>920</v>
       </c>
       <c r="F181" t="s">
         <v>19</v>
@@ -9055,19 +9057,19 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>920</v>
+      </c>
+      <c r="B182" t="s">
         <v>921</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>922</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D182" t="s">
         <v>923</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>924</v>
-      </c>
-      <c r="E182" t="s">
-        <v>925</v>
       </c>
       <c r="F182" t="s">
         <v>19</v>
@@ -9081,19 +9083,19 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>925</v>
+      </c>
+      <c r="B183" t="s">
         <v>926</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>927</v>
       </c>
-      <c r="C183" t="s">
+      <c r="D183" t="s">
         <v>928</v>
       </c>
-      <c r="D183" t="s">
+      <c r="E183" t="s">
         <v>929</v>
-      </c>
-      <c r="E183" t="s">
-        <v>930</v>
       </c>
       <c r="F183" t="s">
         <v>19</v>
@@ -9107,19 +9109,19 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>930</v>
+      </c>
+      <c r="B184" t="s">
         <v>931</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>932</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
         <v>933</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>934</v>
-      </c>
-      <c r="E184" t="s">
-        <v>935</v>
       </c>
       <c r="F184" t="s">
         <v>19</v>
@@ -9133,19 +9135,19 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>935</v>
+      </c>
+      <c r="B185" t="s">
         <v>936</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>937</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D185" t="s">
         <v>938</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>939</v>
-      </c>
-      <c r="E185" t="s">
-        <v>940</v>
       </c>
       <c r="F185" t="s">
         <v>19</v>
@@ -9159,19 +9161,19 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>940</v>
+      </c>
+      <c r="B186" t="s">
         <v>941</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>942</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186" t="s">
         <v>943</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>944</v>
-      </c>
-      <c r="E186" t="s">
-        <v>945</v>
       </c>
       <c r="F186" t="s">
         <v>19</v>
@@ -9185,19 +9187,19 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>945</v>
+      </c>
+      <c r="B187" t="s">
         <v>946</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
         <v>947</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
         <v>948</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>949</v>
-      </c>
-      <c r="E187" t="s">
-        <v>950</v>
       </c>
       <c r="F187" t="s">
         <v>19</v>
@@ -9211,19 +9213,19 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>950</v>
+      </c>
+      <c r="B188" t="s">
         <v>951</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
         <v>952</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
         <v>953</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>954</v>
-      </c>
-      <c r="E188" t="s">
-        <v>955</v>
       </c>
       <c r="F188" t="s">
         <v>19</v>
@@ -9243,54 +9245,54 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>955</v>
+      </c>
+      <c r="B189" t="s">
         <v>956</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>957</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189" t="s">
         <v>958</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>959</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
+        <v>19</v>
+      </c>
+      <c r="H189" t="s">
+        <v>32</v>
+      </c>
+      <c r="J189" t="s">
+        <v>32</v>
+      </c>
+      <c r="L189" t="s">
+        <v>32</v>
+      </c>
+      <c r="M189" t="s">
+        <v>19</v>
+      </c>
+      <c r="N189" t="s">
         <v>960</v>
-      </c>
-      <c r="F189" t="s">
-        <v>19</v>
-      </c>
-      <c r="H189" t="s">
-        <v>32</v>
-      </c>
-      <c r="J189" t="s">
-        <v>32</v>
-      </c>
-      <c r="L189" t="s">
-        <v>32</v>
-      </c>
-      <c r="M189" t="s">
-        <v>19</v>
-      </c>
-      <c r="N189" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>961</v>
+      </c>
+      <c r="B190" t="s">
         <v>962</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>963</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190" t="s">
         <v>964</v>
       </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
         <v>965</v>
-      </c>
-      <c r="E190" t="s">
-        <v>966</v>
       </c>
       <c r="F190" t="s">
         <v>19</v>
@@ -9310,19 +9312,19 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>966</v>
+      </c>
+      <c r="B191" t="s">
         <v>967</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>968</v>
       </c>
-      <c r="C191" t="s">
+      <c r="D191" t="s">
         <v>969</v>
       </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
         <v>970</v>
-      </c>
-      <c r="E191" t="s">
-        <v>971</v>
       </c>
       <c r="F191" t="s">
         <v>19</v>
@@ -9340,24 +9342,24 @@
         <v>19</v>
       </c>
       <c r="N191" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>972</v>
+      </c>
+      <c r="B192" t="s">
         <v>973</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C192" t="s">
         <v>974</v>
       </c>
-      <c r="C192" t="s">
+      <c r="D192" t="s">
         <v>975</v>
       </c>
-      <c r="D192" t="s">
+      <c r="E192" t="s">
         <v>976</v>
-      </c>
-      <c r="E192" t="s">
-        <v>977</v>
       </c>
       <c r="F192" t="s">
         <v>19</v>
@@ -9377,19 +9379,19 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>977</v>
+      </c>
+      <c r="B193" t="s">
         <v>978</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
         <v>979</v>
       </c>
-      <c r="C193" t="s">
+      <c r="D193" t="s">
         <v>980</v>
       </c>
-      <c r="D193" t="s">
+      <c r="E193" t="s">
         <v>981</v>
-      </c>
-      <c r="E193" t="s">
-        <v>982</v>
       </c>
       <c r="F193" t="s">
         <v>19</v>
@@ -9412,86 +9414,86 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>982</v>
+      </c>
+      <c r="B194" t="s">
         <v>983</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>984</v>
       </c>
-      <c r="C194" t="s">
+      <c r="D194" t="s">
         <v>985</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
         <v>986</v>
       </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
+        <v>19</v>
+      </c>
+      <c r="J194" t="s">
+        <v>32</v>
+      </c>
+      <c r="L194" t="s">
+        <v>32</v>
+      </c>
+      <c r="M194" t="s">
+        <v>19</v>
+      </c>
+      <c r="N194" t="s">
         <v>987</v>
-      </c>
-      <c r="F194" t="s">
-        <v>19</v>
-      </c>
-      <c r="J194" t="s">
-        <v>32</v>
-      </c>
-      <c r="L194" t="s">
-        <v>32</v>
-      </c>
-      <c r="M194" t="s">
-        <v>19</v>
-      </c>
-      <c r="N194" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>988</v>
+      </c>
+      <c r="B195" t="s">
         <v>989</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
         <v>990</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195" t="s">
         <v>991</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
         <v>992</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
+        <v>19</v>
+      </c>
+      <c r="I195" t="s">
+        <v>32</v>
+      </c>
+      <c r="J195" t="s">
+        <v>32</v>
+      </c>
+      <c r="L195" t="s">
+        <v>32</v>
+      </c>
+      <c r="M195" t="s">
+        <v>19</v>
+      </c>
+      <c r="N195" t="s">
         <v>993</v>
-      </c>
-      <c r="F195" t="s">
-        <v>19</v>
-      </c>
-      <c r="I195" t="s">
-        <v>32</v>
-      </c>
-      <c r="J195" t="s">
-        <v>32</v>
-      </c>
-      <c r="L195" t="s">
-        <v>32</v>
-      </c>
-      <c r="M195" t="s">
-        <v>19</v>
-      </c>
-      <c r="N195" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>994</v>
+      </c>
+      <c r="B196" t="s">
         <v>995</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>996</v>
       </c>
-      <c r="C196" t="s">
+      <c r="D196" t="s">
         <v>997</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
         <v>998</v>
-      </c>
-      <c r="E196" t="s">
-        <v>999</v>
       </c>
       <c r="F196" t="s">
         <v>19</v>
@@ -9511,19 +9513,19 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>999</v>
+      </c>
+      <c r="B197" t="s">
         <v>1000</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
         <v>1001</v>
       </c>
-      <c r="C197" t="s">
+      <c r="D197" t="s">
         <v>1002</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
         <v>1003</v>
-      </c>
-      <c r="E197" t="s">
-        <v>1004</v>
       </c>
       <c r="F197" t="s">
         <v>19</v>
@@ -9543,19 +9545,19 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B198" t="s">
         <v>1005</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
         <v>1006</v>
       </c>
-      <c r="C198" t="s">
+      <c r="D198" t="s">
         <v>1007</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
         <v>1008</v>
-      </c>
-      <c r="E198" t="s">
-        <v>1009</v>
       </c>
       <c r="F198" t="s">
         <v>19</v>
@@ -9575,19 +9577,19 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B199" t="s">
         <v>1010</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C199" t="s">
         <v>1011</v>
       </c>
-      <c r="C199" t="s">
+      <c r="D199" t="s">
         <v>1012</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
         <v>1013</v>
-      </c>
-      <c r="E199" t="s">
-        <v>1014</v>
       </c>
       <c r="F199" t="s">
         <v>19</v>
@@ -9610,19 +9612,19 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B200" t="s">
         <v>1015</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
         <v>1016</v>
       </c>
-      <c r="C200" t="s">
+      <c r="D200" t="s">
         <v>1017</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" t="s">
         <v>1018</v>
-      </c>
-      <c r="E200" t="s">
-        <v>1019</v>
       </c>
       <c r="F200" t="s">
         <v>19</v>
@@ -9645,19 +9647,19 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B201" t="s">
         <v>1020</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
         <v>1021</v>
       </c>
-      <c r="C201" t="s">
+      <c r="D201" t="s">
         <v>1022</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
         <v>1023</v>
-      </c>
-      <c r="E201" t="s">
-        <v>1024</v>
       </c>
       <c r="F201" t="s">
         <v>19</v>
@@ -9769,19 +9771,19 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>966</v>
+      </c>
+      <c r="B3" t="s">
         <v>967</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>968</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>969</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>970</v>
-      </c>
-      <c r="E3" t="s">
-        <v>971</v>
       </c>
       <c r="F3" t="s">
         <v>19</v>
@@ -9799,7 +9801,7 @@
         <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -9868,19 +9870,19 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>805</v>
+      </c>
+      <c r="B6" t="s">
         <v>806</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>807</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>808</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>809</v>
-      </c>
-      <c r="E6" t="s">
-        <v>810</v>
       </c>
       <c r="F6" t="s">
         <v>19</v>
@@ -9949,19 +9951,19 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>815</v>
+      </c>
+      <c r="B9" t="s">
         <v>816</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>817</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>818</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>819</v>
-      </c>
-      <c r="E9" t="s">
-        <v>820</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
